--- a/backtest_runs/20260410_193731/by_symbol/SBL/SBL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/SBL/SBL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -633,7 +633,7 @@
         <v>-2187.840000000002</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>103099.44</v>
@@ -679,7 +679,7 @@
         <v>-10665.72</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>92433.72</v>
@@ -771,7 +771,7 @@
         <v>-1914.359999999991</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>95715.48000000001</v>
@@ -863,7 +863,7 @@
         <v>-729.2800000000007</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>94986.20000000001</v>
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>94986.20000000001</v>
@@ -1047,7 +1047,7 @@
         <v>-2825.959999999988</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>96171.28000000001</v>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>99179.56000000001</v>
@@ -1185,7 +1185,7 @@
         <v>-7292.800000000007</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>91886.76000000001</v>
@@ -1231,7 +1231,7 @@
         <v>-364.6399999999923</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>91522.12000000002</v>
@@ -1277,7 +1277,7 @@
         <v>-6928.159999999998</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>84593.96000000002</v>
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>88331.52000000002</v>
@@ -1415,7 +1415,7 @@
         <v>-820.4399999999987</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>87511.08000000002</v>
@@ -1507,7 +1507,7 @@
         <v>-1823.199999999993</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>86872.96000000002</v>
@@ -1645,7 +1645,7 @@
         <v>-1002.759999999995</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>95988.96000000002</v>
